--- a/光伏配储项目/电价数据/2026/茅坪站.xlsx
+++ b/光伏配储项目/电价数据/2026/茅坪站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5159900000000001</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.9332699999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.59575</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.7619</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.62936</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.6063</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43759</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45419</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44052</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42287</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42703</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40845</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.3975</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39925</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38394</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40175</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42279</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41161</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35355</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39092</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38448</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41601</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39245</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42163</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41297</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42297</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41254</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44382</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.38336</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30314</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33428</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.25999</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.49177</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.4357</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.24671</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.16921</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.22625</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.25865</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.2847</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.09311</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.19338</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.38435</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.37863</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.29046</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.17697</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.02678</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.23622</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.07820000000000001</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.18362</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.24095</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.26671</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.23037</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.45429</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.06228</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.28832</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.1648</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.38569</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.47875</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.39782</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.5619400000000001</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.06585</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.14593</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.08785</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.49807</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.87627</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.63271</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.5221399999999999</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6056900000000001</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.7310399999999999</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.67499</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.9321200000000001</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.08716</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.80163</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.8573099999999999</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.1971</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.60839</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.90918</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.7586000000000001</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.51403</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.86411</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.7964600000000001</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.84041</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.81463</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.56968</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47945</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40152</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41309</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42234</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.85282</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.79512</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8345900000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.86982</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53607</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5225</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5062300000000001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5374500000000001</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49803</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.41201</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4726</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.3894</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39202</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.3755</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37547</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38045</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42123</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.51937</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.6502599999999999</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7240700000000001</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.44018</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.3836</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.44804</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.58962</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.67604</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.41319</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.51932</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.2931</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.45702</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.38389</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.38797</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.45791</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.66243</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.69887</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.9877899999999999</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.6214</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.67338</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.56176</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.6064299999999999</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.96372</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.71557</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.47255</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.5501699999999999</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.29367</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.45655</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.79244</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.56023</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.48847</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.54804</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.55674</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.39099</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.63425</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.5531</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.47587</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.71238</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.50004</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.98054</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.13885</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.05432</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.87617</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.97405</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.9577100000000001</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.11427</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.8140499999999999</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.88905</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.10138</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.5541</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.31872</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.49399</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.48997</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.6504099999999999</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44073</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43475</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.4181</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37745</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33354</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5156000000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.39325</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.50204</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.39557</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.39389</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40528</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.39529</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38953</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38259</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36188</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43386</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44992</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39348</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36632</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.3709</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35326</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36309</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38022</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47352</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45008</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44426</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34836</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39703</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36837</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.47271</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.3998</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.42824</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.38797</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.44785</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.30127</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30878</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.30282</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.5665</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.5471</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.77285</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.43694</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.65361</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.73783</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.40543</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.39455</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.4654</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.5589500000000001</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.5325599999999999</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.55138</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.55937</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.57801</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.7415700000000001</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.10147</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.64608</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.77423</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.12534</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.59553</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.5377799999999999</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.45962</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.55126</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.8553200000000001</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.8360599999999999</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.77401</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.5157999999999999</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.75805</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.68172</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.92349</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.61642</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.85617</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.6092799999999999</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.6301599999999999</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.61622</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.63142</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.65371</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.59193</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.50276</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.50849</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.42098</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35799</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34312</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5851499999999999</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.4866</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39909</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.42131</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39979</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.37854</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.31665</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46678</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.31667</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.32686</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.30455</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.30455</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.30283</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.30031</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.30187</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35782</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38918</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.32597</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.33745</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34352</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.41814</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.49273</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.46224</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.47313</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.43116</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.69899</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.70184</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.46607</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.5797100000000001</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.55049</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.27022</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.23283</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.38472</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.45525</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.67722</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.25843</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.33843</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.45819</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.44044</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.45084</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.41479</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.4174</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.37664</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.63686</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.4014</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.7656499999999999</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.3972</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.40778</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.44933</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.41565</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.45659</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.5302899999999999</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.51837</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.5794900000000001</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.54676</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.7586499999999999</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.53315</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50448</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.43652</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.45064</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.46631</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.47154</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.44193</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.43441</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.38018</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.32593</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31553</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.38444</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30769</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.30179</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.2999</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.35633</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.40039</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38695</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35779</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30585</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31524</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30846</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.29238</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30817</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30644</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29515</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29371</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29421</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29511</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.30081</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29525</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29762</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31251</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30651</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.28597</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26996</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.10229</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.10216</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.10449</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.08276</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.07836</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.08769</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.08120999999999999</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.09644</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.00661</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.01187</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.04649</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.06238</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.03474</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.04498</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.00175</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.04851</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.00115</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.02708</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.02614</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.02298</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.03035</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.01323</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21263</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.08069</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.08245999999999999</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.08604000000000001</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.00537</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.00113</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.04025</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.00264</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.20166</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.10173</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.15855</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.36927</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.34301</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.35269</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.39783</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39246</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.39918</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37557</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39956</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39843</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.4099</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.45286</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.37178</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.74541</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.47909</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.52139</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.44659</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.44298</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.36507</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.36669</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.36384</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33134</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33613</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30465</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34246</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.12826</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04724</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04658</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.00085</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.0457</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04534000000000001</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.0457</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04485</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04163</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.03193</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.12524</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.0094</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04333</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.01005</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.0213</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.0428</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04488</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04485</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.03692</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04229</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04455</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04205</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04229</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.00067</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04446</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04476</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04245</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.00074</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.00101</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.04987</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.00091</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.00139</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.00048</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.00238</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.00276</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.22415</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.17979</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.30793</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.30877</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.30655</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.30952</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.28345</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.30915</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35574</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35274</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36751</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33624</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.33375</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40554</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30987</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30438</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28642</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29833</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29389</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28607</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27692</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27602</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28525</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.19011</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.17779</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1718</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16014</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15938</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23744</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.2148</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.23691</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27433</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28946</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.2945</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29514</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28632</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28681</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28644</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27548</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28686</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.3139</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.43799</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.3704</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.42689</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.43682</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.50345</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45542</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.42478</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.45979</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.44133</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.47349</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15409</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29153</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.39889</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.37748</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.41754</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47938</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.54104</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79227</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6463099999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.4303</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.5347999999999999</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.8171499999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.99378</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.54722</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.99785</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.96217</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.38446</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.4354</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.9774299999999999</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.69589</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.29499</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.9555</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.80136</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.41201</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.1057</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.58311</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.80553</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303600000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7878099999999999</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78914</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8786</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.88151</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50681</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.4122</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41747</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46556</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.22458</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.8793800000000001</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.63952</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5426799999999999</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50264</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45791</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42625</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44019</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45069</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39257</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45284</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42074</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38935</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39063</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35354</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40661</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.4509</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39783</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58904</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.4291</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59624</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.59735</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66118</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.5271699999999999</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.44366</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.56516</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.46598</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.94851</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.68148</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.9026000000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.8839900000000001</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.9014</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.47609</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.36786</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.41603</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.49102</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.45303</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.40487</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.54188</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.38257</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.36527</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.38872</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.35562</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.36852</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.36346</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.37802</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.36174</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.38642</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.37107</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.39654</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.3815</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.37794</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.37419</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.36059</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.42219</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41258</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45231</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41493</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39145</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35327</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.95651</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.47709</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40812</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.48303</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.54571</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.39269</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40968</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.39213</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.41496</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.38399</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38588</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50008</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38769</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.38809</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.35832</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.38919</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.41319</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.3638</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.21995</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.39055</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.38691</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.42054</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.38609</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.3737200000000001</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.22414</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.31246</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.27043</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.29043</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.5032799999999999</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.43353</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.37544</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.44435</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.3899</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.38111</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.47652</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.36823</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.30585</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.33299</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29776</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.26677</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.30076</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35377</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.29105</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.29371</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.25116</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.3067</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32229</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.36579</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.05194</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43249</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.29182</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35891</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40172</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40045</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59676</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.92867</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.4261</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.18814</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7036399999999999</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7954</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6498200000000001</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58369</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45042</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42355</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.55602</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.3767</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.41012</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.61276</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.47559</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.43441</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.4897</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.35562</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.49462</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.7980700000000001</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.6767300000000001</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.54995</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.42188</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.7216900000000001</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.73309</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.41555</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.6349600000000001</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.64134</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.45685</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.28466</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.30572</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.43058</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.44134</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.39747</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.39672</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.39275</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.44138</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.43358</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.41865</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.45411</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.5475599999999999</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.48457</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.44279</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.47276</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.42941</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.43073</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.5246900000000001</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.47871</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.45008</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.48624</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.4417</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.42934</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.73358</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.55588</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.8860399999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.63015</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.51612</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.46874</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.4702</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38652</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36961</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32474</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42503</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32746</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39153</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.92428</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.26356</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.17775</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.18136</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.19159</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.56929</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.5815499999999999</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.16847</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.17335</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.1867</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.18493</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.29231</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.19339</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.30313</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.18233</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.17373</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.16314</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.16585</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.19865</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.18993</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.17962</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.3083399999999999</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.33895</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.39819</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.37386</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36143</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40506</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40023</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44973</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39355</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40189</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39773</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44311</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43993</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4393</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44422</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44428</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40268</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39055</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39773</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39161</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34935</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5424500000000001</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38909</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.4687</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42387</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41594</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.3811</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38022</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39309</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36989</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39109</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37024</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38027</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34477</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38011</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37565</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28908</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28615</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28466</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.29819</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26053</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>-0.03006</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.27482</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.25527</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.22901</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.24992</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.2981</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28873</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.29072</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30325</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30077</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.2843</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.26043</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30829</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31112</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.29996</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.30481</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.43032</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.40793</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.39969</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.44656</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.5394800000000001</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.5210900000000001</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.45613</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.37469</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.35891</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.44507</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.4912</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.54635</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.55199</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.42067</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.39967</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.39498</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.37253</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.36645</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.36066</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.4195</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39278</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.38395</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.38856</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.38148</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.37768</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36026</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41861</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.43939</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38047</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33814</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.39054</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.44435</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.50742</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.51491</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.50362</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.506</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.67355</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.66073</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.45652</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.55953</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.7812899999999999</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.48641</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.7655</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.64547</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.6381699999999999</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.7056</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.17837</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.52349</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27132</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.7295</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.25765</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.48721</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.30668</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.52334</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.49687</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.63775</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.6208400000000001</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.65423</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.66757</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.66269</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.63986</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.66432</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.5616</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.6974600000000001</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.7966</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.77878</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.7489199999999999</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.69438</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.7021000000000001</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.7101900000000001</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.65962</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.7444700000000001</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.49414</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.52616</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.6882</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.69656</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.69048</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.9454</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.76988</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.08656</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.7200800000000001</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.80877</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.47248</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.42138</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.34047</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.04601</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.73397</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.52473</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34185</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.37506</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.3097</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.38798</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.5342899999999999</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.33774</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.33774</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33872</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32518</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.54961</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.5540900000000001</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.43774</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.36412</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.3756</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.37249</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.28902</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34231</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29831</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.2815299999999999</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32185</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.37756</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.47479</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.60952</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.5531699999999999</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.49086</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.43968</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.36951</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.34824</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.38656</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.37254</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.37621</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.37531</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.40767</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36762</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36148</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36778</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37309</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39286</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40287</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36942</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34931</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.3354</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29251</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.35633</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.4387200000000001</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.37749</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.70461</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.37495</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.34513</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.35702</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33834</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.37635</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5624</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38911</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.37486</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.39135</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.3512</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.37158</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.46091</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.3996</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.40121</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42962</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40916</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38572</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38502</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65198</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83086</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47177</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40089</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45943</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34477</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41079</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37584</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35678</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37946</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.28394</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.38749</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.29313</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.29193</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.21969</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28844</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.01162</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.24542</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29734</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.22183</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.02005</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.18574</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.30879</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.04237</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.30815</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.27363</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.44294</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.44461</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.53762</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.35933</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.4788</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.50615</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.9306</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.47419</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.91235</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.30386</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.25383</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.76164</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.58766</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>1.38794</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.45209</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.97504</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.51044</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>1.72614</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>1.38161</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.9848300000000001</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.88046</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.54872</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.59149</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.6053500000000001</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43005</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41896</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37806</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36015</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.54195</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.7443</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.65828</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.89547</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41943</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40472</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40494</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41137</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40905</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41775</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39588</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41166</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40939</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39366</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38712</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.4185</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38727</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41663</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39008</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39991</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39986</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41249</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39991</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45051</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44949</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5606100000000001</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50066</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45069</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.41859</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.79062</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.7692100000000001</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.04466</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.11209</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.21319</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.32061</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.27718</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.14178</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.66267</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.6932</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.78247</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.5492400000000001</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.5394</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.55401</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37061</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.00255</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>-0.01661</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.20452</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.26877</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.94759</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.60362</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.73531</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.3728</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.00838</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.56443</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.50418</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.41812</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.59008</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.2834</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.45555</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.56541</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.36601</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.36899</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.41135</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.40009</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.46372</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.5387999999999999</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.44608</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.51544</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.43344</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.5297000000000001</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.5734199999999999</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.72754</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.67574</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.6363099999999999</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.6374500000000001</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.6182300000000001</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.7567</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.00742</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.4474</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.12626</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.04833</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.80541</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.38611</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.8497100000000001</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.78526</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6364500000000001</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.00761</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.6437999999999999</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.71817</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.58815</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47842</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47175</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.4194</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.55559</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.40333</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.40283</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45814</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.4368</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42656</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44837</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41783</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45771</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39934</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40704</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39863</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38854</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37486</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37679</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38658</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.4089100000000001</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.40185</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.39098</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.4372</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39449</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38659</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.42451</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.41651</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.43184</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.43739</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.57469</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.68047</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.14193</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.1885</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.19921</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.36899</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.03577</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29912</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.36538</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.4054700000000001</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.40252</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.41544</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.43374</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.42007</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36371</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41308</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41642</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.4455</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.42647</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.4493</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38071</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38622</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40611</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40196</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36548</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39923</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38079</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39388</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36415</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.50359</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.50483</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.45898</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.4301</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37715</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37706</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.37275</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.36403</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.25314</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.30437</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.24727</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.26417</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.03639</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.18981</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.28827</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29635</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.06584999999999999</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.17933</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04336</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.27639</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.02572</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18763</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.05987</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.01348</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.23979</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.24806</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.17158</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23239</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27832</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.2702</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.31351</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30352</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.36854</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.4202</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.39094</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.41088</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.39578</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.36652</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.41068</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.36973</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.42426</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.37661</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39532</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.38781</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.39267</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.38406</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.41313</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34735</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36514</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36984</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36533</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.3517</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.4055</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34413</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.35577</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31028</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30616</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30742</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29631</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.25748</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.25086</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.16834</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.20683</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.45218</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.08656999999999999</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.07219</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.0319</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.01992</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.18736</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.03247</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.03112</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.01807</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.11156</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.18069</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.12042</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.04383</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.03391</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.0322</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.11027</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.01639</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.02283</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.0187</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.01654</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.02516</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.08108</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.04984</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.0162</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.0188</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.01622</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.01557</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.02882</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.01918</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.05221</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.03442</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.16666</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.20568</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.25047</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.29359</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.27328</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.27734</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.2706</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.27549</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.28823</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.31001</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.29306</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.29579</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28376</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31184</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30116</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.30308</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29209</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.3045</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.29169</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30658</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29655</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.45207</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.30277</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.27805</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.28606</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.2736</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.26364</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.22475</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.12426</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29965</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.5242100000000001</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.24745</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.15437</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.27413</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.30471</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.2432</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.28841</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.27502</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.25553</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.23838</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.22559</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.24419</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.25089</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.21286</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.2465</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.24397</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.25557</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.2663</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.26508</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.24358</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.2844100000000001</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.25858</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.29881</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.39566</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.29986</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.27135</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.21969</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.13839</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.60375</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.60677</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.71827</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.5647000000000001</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.28246</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.45007</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.14722</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.2628</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.1453</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.11339</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>1.06605</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.14741</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.27494</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.14148</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31304</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.11731</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.01842</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.1151</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.17335</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.04622</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.19635</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.03075</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.13567</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.27932</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.22976</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.07987000000000001</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.17289</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30545</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.4732</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.16594</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.3969</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.38799</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.5097699999999999</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.47081</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.48798</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.4882</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.48731</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.52565</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.41396</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.50751</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.42809</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.5304800000000001</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.90401</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.67215</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.65642</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.69041</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.8063400000000001</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.67261</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.69855</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.7082999999999999</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.7969700000000001</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.5444</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.49895</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.5410700000000001</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.53992</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.64375</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.55247</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.46662</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.34482</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.40978</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.3288</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.39377</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.45071</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.41664</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.41663</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.37454</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.13828</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.33415</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.33866</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.34735</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.34733</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.35789</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.9606</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.76158</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.66242</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.6124700000000001</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.49263</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.5792</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.49744</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.43565</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.02383</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.6132300000000001</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.52574</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.6162300000000001</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.68053</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.67513</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.53687</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.55467</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.44536</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.40995</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.1603</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.28469</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.2204</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.38389</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.55611</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.15815</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.3561</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.36716</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.37219</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.38716</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.39202</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.38527</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.37124</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.37889</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.35328</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.38722</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.40324</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.39245</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.42538</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.5396599999999999</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.53574</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.42703</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.3651</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.7554099999999999</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.48643</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.48588</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.54752</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.52411</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.40865</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.41015</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.39878</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.38177</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.3864</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33328</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.36178</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.30533</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35543</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36911</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.37298</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.42455</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.55096</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.43231</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.5366799999999999</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.77035</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.66362</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.88976</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.9952000000000001</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.38197</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.49414</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.5304500000000001</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.47653</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.45021</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.48395</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.46287</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.45158</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.27317</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.45475</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.61242</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.44598</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.47462</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.47258</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.15842</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.45441</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.40872</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.46604</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.4928</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.48526</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.51286</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.6225599999999999</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.6451399999999999</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.69202</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.7585599999999999</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.74175</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.81177</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.82426</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.80199</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.6898200000000001</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.5939800000000001</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.57847</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.47262</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.69308</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.53067</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.6036699999999999</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.53251</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.5694</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.5448</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.50728</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.5326900000000001</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42415</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.68372</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.50115</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40152</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45846</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.45625</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.4997200000000001</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.47166</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36271</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36868</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.55951</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.4012</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40124</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39191</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37441</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37729</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37576</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.37682</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.39272</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.47023</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.39113</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.6001299999999999</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.59981</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.57829</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.6564500000000001</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.6647999999999999</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.56975</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.67508</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.7427</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.50674</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.5067</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.51487</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.4976</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.49771</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.25158</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.25754</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.27624</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.47468</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.45671</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32384</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34156</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.42366</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.19737</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.47414</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.54588</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.5280900000000001</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.40769</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.57923</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.5815900000000001</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.41792</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.6025199999999999</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.42149</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.40312</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.43506</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.7077899999999999</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.63224</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.5891799999999999</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.5699500000000001</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.46402</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.53753</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5233</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.5237999999999999</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.45593</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.54661</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.53183</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.28399</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.66059</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.52743</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.49334</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.47167</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.37521</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.74814</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.5150399999999999</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5168200000000001</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39829</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.49345</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.47172</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.43346</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.3825</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36945</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37505</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27079</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.37096</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.40037</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31498</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.30424</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.38295</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.30282</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.29789</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.29368</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.28691</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.32663</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.42024</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.38686</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.31665</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.34305</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.55937</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.45725</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.7536499999999999</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.24736</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.17845</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.12729</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.7452300000000001</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.64198</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.1638</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.06222</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.01428</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.08603</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.05571</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.24262</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.00232</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.18449</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.08466</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.18948</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.1746</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.1277</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.28552</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.30311</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.23568</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.48691</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.49857</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.38131</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.30077</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.43666</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.51332</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.5654400000000001</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.43889</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.45162</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.35829</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.43311</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.4437</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.17674</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.04881</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.27583</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.29488</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.4171</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.42851</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.50242</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.48278</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.48786</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.5169199999999999</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.50103</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.48283</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.61529</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.47423</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.49659</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.4474</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.43355</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.38364</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37532</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.98595</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.48659</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.54279</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.58296</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.45079</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.38233</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.36135</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.3845</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.35372</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.3786600000000001</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35839</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36488</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.37997</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36224</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36376</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36549</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38332</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.40115</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.31324</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.41257</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.39738</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.39363</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36548</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.39913</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.51371</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.29484</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.26723</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.30149</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.20858</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.4072</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.24541</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.0655</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.07315000000000001</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.11701</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.06906</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.13355</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.38715</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.21271</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.30477</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.26288</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.38854</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.18838</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.27458</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>1.13385</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.8942100000000001</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.80738</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.40492</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.61738</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.04114</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.09153</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.9877</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.82397</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.55763</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.48191</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.6791799999999999</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.69296</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.52212</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.66591</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.54225</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5757100000000001</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.56698</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.5504199999999999</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.68776</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.59437</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.5951799999999999</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.59992</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.70916</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.5203300000000001</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.54353</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.48971</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.56469</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.6491699999999999</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.69021</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.5282100000000001</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.42368</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.39812</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.40109</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33326</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.65677</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.42924</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.43222</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.38485</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.37882</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.37837</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.36318</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41964</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.38664</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37333</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32445</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.31124</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.27403</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.24838</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.23094</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.1594</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.21282</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.28139</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.25169</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.21491</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.28167</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.19918</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.18049</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.21423</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.21092</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.19876</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.11982</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14085</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.13446</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.18693</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.14915</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.26167</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.21929</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.10493</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.32577</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.17883</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.19135</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.26199</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.19945</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.46534</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.28647</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.28574</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.3633</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.37406</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.37595</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.37922</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.39047</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.43565</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.46056</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.41572</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.42367</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.51131</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.46067</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.44635</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.42305</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.43237</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.53459</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.5573899999999999</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.50197</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.4366</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.44494</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.42069</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.40208</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40849</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40967</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38407</v>
       </c>
     </row>
   </sheetData>
